--- a/reports/feb25 to jan26/Liability/Current Liabilities/Salary Payable/GrpSum.xlsx
+++ b/reports/feb25 to jan26/Liability/Current Liabilities/Salary Payable/GrpSum.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc31808bb1f3f1ad/MANGEMENT FILE/Documents/Antigravity/Wilmer House/reports/feb25 to jan26/Liability/Current Liabilities/Salary Payable/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Antigravity\Wilmer House\reports\feb25 to jan26 - Copy\Liability\Current Liabilities\Salary Payable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0742824C-E570-4D60-B391-4C5014021037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4D2E63-D095-478A-BD27-7F688874749B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="20" windowWidth="18750" windowHeight="10180" xr2:uid="{3B846E4B-8132-437B-8064-91E9BDAAB9F7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="990" xr2:uid="{3B846E4B-8132-437B-8064-91E9BDAAB9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Salary Payable" sheetId="1" r:id="rId1"/>
+    <sheet name="Nayankumar Godhani Salary Payab" sheetId="2" r:id="rId2"/>
+    <sheet name="Parth Kumar Salary Payable" sheetId="3" r:id="rId3"/>
+    <sheet name="Pinal Godhani Salary Payable" sheetId="4" r:id="rId4"/>
+    <sheet name="Salil Anand Salary Payable" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="96">
   <si>
     <t>WILMER HOUSE LTD</t>
   </si>
@@ -85,6 +89,243 @@
   </si>
   <si>
     <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Ledger Account</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Vch Type</t>
+  </si>
+  <si>
+    <t>Vch No.</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>WILMER HOUSE LTD Bank</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>By</t>
+  </si>
+  <si>
+    <t>Nayankumar Godhani Salary</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>Closing Balance</t>
+  </si>
+  <si>
+    <t>Opening Balance</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Parth Kumar Salary</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Pinal Godhani Salary</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Salil Anand Salary</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>229</t>
   </si>
 </sst>
 </file>
@@ -97,7 +338,7 @@
     <numFmt numFmtId="166" formatCode="&quot;&quot;0.00&quot; Cr&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;&quot;0.00&quot; Dr&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +383,13 @@
       <b/>
       <i/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -233,81 +481,150 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="8"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="8"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -634,184 +951,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="37"/>
+      <c r="E8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
         <v>1221</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="12">
         <v>2661.78</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="13">
         <v>1440.78</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="13">
         <v>220.8</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="12">
         <v>13680.39</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="12">
         <v>13364.72</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="14">
         <v>94.87</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12">
         <v>1221</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="12">
         <v>1660.56</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="13">
         <v>439.56</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="13">
         <v>1409.74</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="12">
         <v>18339.63</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="12">
         <v>17921.43</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="13">
         <v>991.54</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="16">
         <v>1630.54</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="17">
         <v>34462.019999999997</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="17">
         <v>35608.49</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="16">
         <v>2777.01</v>
       </c>
     </row>
@@ -829,4 +1146,2051 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC42B9B0-5E3F-4D50-BAC4-5D9CD739E93B}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
+        <v>45898</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="25">
+        <v>219.78</v>
+      </c>
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>45900</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>45961</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="25">
+        <v>1001.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
+        <v>46044</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1001.22</v>
+      </c>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
+        <v>46053</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="25">
+        <v>1001.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="44">
+        <v>1221</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="27">
+        <v>2661.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="45">
+        <v>1440.78</v>
+      </c>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="31"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="46">
+        <v>2661.78</v>
+      </c>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="32">
+        <v>2661.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC696E75-6430-45CF-8D82-99529112C114}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="33">
+        <v>45689</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="25">
+        <v>220.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>45698</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="25">
+        <v>473</v>
+      </c>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>45716</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="25">
+        <v>377.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>45730</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="25">
+        <v>220</v>
+      </c>
+      <c r="G11" s="26"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>45747</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
+        <v>45748</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="25">
+        <v>368</v>
+      </c>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
+        <v>45777</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="25">
+        <v>390.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
+        <v>45784</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="25">
+        <v>390.8</v>
+      </c>
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
+        <v>45807</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="25">
+        <v>781.4</v>
+      </c>
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
+        <v>45808</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="25">
+        <v>781.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="21">
+        <v>45838</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="25">
+        <v>1477.66</v>
+      </c>
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="21">
+        <v>45838</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="26"/>
+      <c r="G19" s="25">
+        <v>1477.69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
+        <v>45866</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="25">
+        <v>1094.83</v>
+      </c>
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
+        <v>45869</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="25">
+        <v>1094.83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
+        <v>45898</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="25">
+        <v>2173.41</v>
+      </c>
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
+        <v>45900</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="25">
+        <v>2173.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="25">
+        <v>2051.88</v>
+      </c>
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="26"/>
+      <c r="G25" s="25">
+        <v>2051.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="21">
+        <v>45960</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="25">
+        <v>1154.8900000000001</v>
+      </c>
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
+        <v>45961</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="26"/>
+      <c r="G27" s="25">
+        <v>1154.8900000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
+        <v>45991</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="26"/>
+      <c r="G28" s="25">
+        <v>1067.1600000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
+        <v>45993</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="25">
+        <v>1067.1600000000001</v>
+      </c>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="25">
+        <v>991</v>
+      </c>
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="26"/>
+      <c r="G31" s="25">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="21">
+        <v>46052</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="25">
+        <v>1300</v>
+      </c>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="21">
+        <v>46052</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="25">
+        <v>136.36000000000001</v>
+      </c>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
+        <v>46053</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="25">
+        <v>1436.36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="44">
+        <v>13680.39</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="27">
+        <v>13585.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="30">
+        <v>94.87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="46">
+        <v>13680.39</v>
+      </c>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="32">
+        <v>13680.39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A37:F37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0D4F97-CD9C-4195-950C-FB1C047F4675}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
+        <v>45898</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="25">
+        <v>219.78</v>
+      </c>
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>45900</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="G9" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>45961</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="25">
+        <v>219.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="25">
+        <v>1001.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
+        <v>46034</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1001.22</v>
+      </c>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="44">
+        <v>1221</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="27">
+        <v>1660.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="45">
+        <v>439.56</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="31"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="46">
+        <v>1660.56</v>
+      </c>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="32">
+        <v>1660.56</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAA2328-91DA-4A41-AB5B-7AF62AB4941D}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="33">
+        <v>45689</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="25">
+        <v>1409.74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>45698</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="25">
+        <v>409.74</v>
+      </c>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>45716</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="25">
+        <v>1409.73</v>
+      </c>
+      <c r="G10" s="26"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>45716</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="25">
+        <v>1409.73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>45747</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="25">
+        <v>1200</v>
+      </c>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
+        <v>45747</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="26"/>
+      <c r="G13" s="25">
+        <v>1409.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
+        <v>45748</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="25">
+        <v>209.54</v>
+      </c>
+      <c r="G14" s="26"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
+        <v>45777</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="25">
+        <v>1543.07</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
+        <v>45778</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="25">
+        <v>1543.07</v>
+      </c>
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
+        <v>45807</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="25">
+        <v>1543.07</v>
+      </c>
+      <c r="G17" s="26"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="21">
+        <v>45808</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="26"/>
+      <c r="G18" s="25">
+        <v>1543.07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="21">
+        <v>45838</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="25">
+        <v>1542.87</v>
+      </c>
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
+        <v>45838</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="26"/>
+      <c r="G20" s="25">
+        <v>1542.87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
+        <v>45868</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="25">
+        <v>1543.07</v>
+      </c>
+      <c r="G21" s="26"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
+        <v>45869</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="25">
+        <v>1543.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
+        <v>45898</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="25">
+        <v>1542.87</v>
+      </c>
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>45900</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="26"/>
+      <c r="G24" s="25">
+        <v>1542.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="25">
+        <v>1543.07</v>
+      </c>
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="21">
+        <v>45930</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="26"/>
+      <c r="G26" s="25">
+        <v>1543.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
+        <v>45961</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="25">
+        <v>1543.07</v>
+      </c>
+      <c r="G27" s="26"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
+        <v>45961</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="26"/>
+      <c r="G28" s="25">
+        <v>1543.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
+        <v>45989</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="25">
+        <v>1500</v>
+      </c>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="21">
+        <v>45991</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="26"/>
+      <c r="G30" s="25">
+        <v>1481.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="25">
+        <v>1400</v>
+      </c>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="21">
+        <v>46022</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="26"/>
+      <c r="G32" s="25">
+        <v>1409.74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="21">
+        <v>46052</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="25">
+        <v>1409.53</v>
+      </c>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
+        <v>46053</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="25">
+        <v>1409.53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="44">
+        <v>18339.63</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="27">
+        <v>19331.169999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="45">
+        <v>991.54</v>
+      </c>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="31"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="46">
+        <v>19331.169999999998</v>
+      </c>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="32">
+        <v>19331.169999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A37:F37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>